--- a/web/public/forms/orig/o-gaseol-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-gaseol-gyehoekseo.xlsx
@@ -937,7 +937,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -1916,7 +1916,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="Z1" s="82" t="inlineStr">
@@ -3197,7 +3197,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -5785,7 +5785,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -6222,7 +6222,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -7061,7 +7061,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -8493,7 +8493,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">
@@ -10531,7 +10531,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -11367,7 +11367,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="Z1" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -15058,7 +15058,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -15490,7 +15490,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -16204,7 +16204,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -17631,7 +17631,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -19640,7 +19640,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="82" t="inlineStr">

--- a/web/public/forms/orig/o-gaseol-gyehoekseo.xlsx
+++ b/web/public/forms/orig/o-gaseol-gyehoekseo.xlsx
@@ -905,7 +905,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1853,7 +1853,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="Z1" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -7638,7 +7638,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
